--- a/data/trans_bre/P19C04-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,56; -2,88</t>
+          <t>-13,07; -3,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-17,97; -8,3</t>
+          <t>-18,31; -8,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -2,23</t>
+          <t>-11,84; -2,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,84; -2,54</t>
+          <t>-11,42; -2,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,38; -14,91</t>
+          <t>-53,63; -19,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-53,45; -29,2</t>
+          <t>-54,62; -29,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,26; -12,63</t>
+          <t>-47,83; -11,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,37; -13,55</t>
+          <t>-43,8; -14,48</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,72; -4,97</t>
+          <t>-12,61; -4,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,19; -2,6</t>
+          <t>-10,69; -2,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,24</t>
+          <t>-6,63; 0,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 6,42</t>
+          <t>-2,94; 6,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,61; -26,26</t>
+          <t>-54,02; -26,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,76; -9,62</t>
+          <t>-37,36; -11,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 1,55</t>
+          <t>-36,46; 3,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 96,98</t>
+          <t>-20,15; 100,94</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 2,26</t>
+          <t>-7,29; 2,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,38; -4,41</t>
+          <t>-13,49; -3,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,64; -3,26</t>
+          <t>-11,89; -3,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -1,03</t>
+          <t>-9,65; -1,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 13,44</t>
+          <t>-31,96; 12,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,19; -19,52</t>
+          <t>-49,7; -17,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-54,38; -18,38</t>
+          <t>-55,24; -19,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,52; -12,28</t>
+          <t>-71,34; -10,7</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,75</t>
+          <t>-5,83; 1,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 2,06</t>
+          <t>-5,48; 2,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 0,19</t>
+          <t>-6,88; 0,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -3,37</t>
+          <t>-9,5; -3,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 10,68</t>
+          <t>-30,49; 12,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 12,37</t>
+          <t>-26,08; 14,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 1,66</t>
+          <t>-38,08; 5,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,41; -23,77</t>
+          <t>-53,8; -25,3</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -3,19</t>
+          <t>-7,22; -3,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,28; -4,76</t>
+          <t>-9,4; -4,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -3,01</t>
+          <t>-6,92; -3,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -0,7</t>
+          <t>-6,44; -1,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,32; -17,24</t>
+          <t>-34,5; -17,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,81; -20,37</t>
+          <t>-35,84; -21,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-37,62; -17,67</t>
+          <t>-36,4; -17,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-39,83; -8,22</t>
+          <t>-40,93; -10,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C04-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,92</t>
+          <t>-7,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-30,87%</t>
+          <t>-32,37%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,07; -3,69</t>
+          <t>-13,01; -3,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,31; -8,41</t>
+          <t>-18,51; -8,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -2,4</t>
+          <t>-11,63; -1,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,42; -2,96</t>
+          <t>-11,34; -3,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,63; -19,55</t>
+          <t>-52,51; -18,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,62; -29,91</t>
+          <t>-54,12; -29,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,83; -11,44</t>
+          <t>-47,77; -9,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,8; -14,48</t>
+          <t>-45,4; -17,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>-17,8%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,61; -4,99</t>
+          <t>-12,44; -4,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,69; -2,79</t>
+          <t>-10,83; -2,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 0,5</t>
+          <t>-6,51; 0,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 6,24</t>
+          <t>-5,24; 0,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,02; -26,2</t>
+          <t>-53,41; -25,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-37,36; -11,25</t>
+          <t>-38,14; -9,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 3,7</t>
+          <t>-36,66; 3,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 100,94</t>
+          <t>-32,49; 0,91</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,4</t>
+          <t>-3,07</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-40,19%</t>
+          <t>-25,9%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,13</t>
+          <t>-7,51; 1,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,49; -3,74</t>
+          <t>-12,97; -4,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,89; -3,32</t>
+          <t>-11,79; -2,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,65; -1,0</t>
+          <t>-6,37; 0,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 12,24</t>
+          <t>-33,59; 10,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,7; -17,01</t>
+          <t>-48,21; -18,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,24; -19,88</t>
+          <t>-54,27; -15,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,34; -10,7</t>
+          <t>-45,25; 2,68</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,49</t>
+          <t>-7,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-40,08%</t>
+          <t>-40,26%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,94</t>
+          <t>-5,91; 1,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 2,3</t>
+          <t>-5,28; 2,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 0,74</t>
+          <t>-6,84; 0,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,5; -3,69</t>
+          <t>-10,38; -4,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 12,24</t>
+          <t>-29,66; 11,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,08; 14,33</t>
+          <t>-26,07; 13,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 5,23</t>
+          <t>-37,85; 3,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,8; -25,3</t>
+          <t>-51,7; -26,42</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-4,86</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-27,28%</t>
+          <t>-29,71%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -3,2</t>
+          <t>-7,41; -3,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -4,93</t>
+          <t>-9,42; -5,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -3,01</t>
+          <t>-6,86; -2,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -1,1</t>
+          <t>-6,35; -3,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-34,5; -17,02</t>
+          <t>-34,97; -16,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-35,84; -21,28</t>
+          <t>-36,04; -21,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,4; -17,75</t>
+          <t>-36,39; -17,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-40,93; -10,96</t>
+          <t>-36,63; -21,18</t>
         </is>
       </c>
     </row>
